--- a/GraficosGuardianClima.xlsx
+++ b/GraficosGuardianClima.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Consultas por Ciudad" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Temperatura por Ciudad" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Temperatura Buenos Aires" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Condiciones Climaticas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -66,18 +66,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
     </border>
     <border>
       <bottom style="thin">
@@ -93,13 +88,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -262,6 +257,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -274,12 +270,13 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>N° de Consultas</a:t>
+                  <a:t>N de Consultas</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -307,7 +304,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Temperatura por Ciudad en el Tiempo</a:t>
+              <a:t>Temperatura en Buenos Aires</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -323,12 +320,16 @@
             <v>Buenos Aires</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln w="25000">
+              <a:solidFill>
+                <a:srgbClr val="2E6DA4"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="6"/>
             <spPr>
               <a:ln>
                 <a:prstDash val="solid"/>
@@ -337,167 +338,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Temperatura por Ciudad'!$A$3:$A$17</f>
+              <f>'Temperatura Buenos Aires'!$A$3:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Temperatura por Ciudad'!$B$2:$B$17</f>
-            </numRef>
-          </val>
-          <smooth val="1"/>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <v>Estonia</v>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Temperatura por Ciudad'!$A$3:$A$17</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Temperatura por Ciudad'!$C$2:$C$17</f>
-            </numRef>
-          </val>
-          <smooth val="1"/>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <v>Lima</v>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Temperatura por Ciudad'!$A$3:$A$17</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Temperatura por Ciudad'!$D$2:$D$17</f>
-            </numRef>
-          </val>
-          <smooth val="1"/>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <v>Londres</v>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Temperatura por Ciudad'!$A$3:$A$17</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Temperatura por Ciudad'!$E$2:$E$17</f>
-            </numRef>
-          </val>
-          <smooth val="1"/>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <v>Moscu</v>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Temperatura por Ciudad'!$A$3:$A$17</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Temperatura por Ciudad'!$F$2:$F$17</f>
-            </numRef>
-          </val>
-          <smooth val="1"/>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <v>Paris</v>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Temperatura por Ciudad'!$A$3:$A$17</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Temperatura por Ciudad'!$G$2:$G$17</f>
+              <f>'Temperatura Buenos Aires'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="1"/>
@@ -547,7 +393,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Temperatura (°C)</a:t>
+                  <a:t>Temperatura (C)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -660,12 +506,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="5760000"/>
+    <ext cx="8640000" cy="5400000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1003,7 +849,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1021,7 +867,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>N° Consultas</t>
+          <t>N de Consultas</t>
         </is>
       </c>
     </row>
@@ -1100,22 +946,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Temperatura a lo Largo del Tiempo</t>
+          <t>Temperatura en Buenos Aires a lo Largo del Tiempo</t>
         </is>
       </c>
     </row>
@@ -1127,293 +969,123 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Temperatura (C)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Estonia</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Lima</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Londres</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Moscu</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Paris</t>
+          <t>Condicion</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:43:13</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n"/>
+          <t>2026-05-25 14:44:02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Cloudy</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:43:42</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="n"/>
+          <t>2026-05-25 14:52:13</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Cloudy</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:44:02</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
+          <t>2026-05-25 15:20:10</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Cloudy</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:52:13</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+          <t>2026-05-25 15:21:12</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Cloudy</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:58:55</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="n"/>
+          <t>2026-05-28 16:03:59</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Overcast</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-25 15:20:10</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
+          <t>2026-05-28 16:30:04</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Overcast</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25 15:20:29</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-25 15:21:12</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-28 16:03:59</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-28 16:20:12</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-28 16:20:18</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-28 16:20:27</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-28 16:20:58</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-28 16:30:04</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
           <t>2026-05-28 16:44:42</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
+      <c r="B9" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Overcast</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
